--- a/Deterministic/Model Files/Segment Test/data/producer_ratios.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/producer_ratios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Model Files/L-Shaped/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{243B714B-BD6B-4548-BBF5-8AECB1072816}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2908E804-5211-4722-A2E4-9417D4B1AE86}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
@@ -692,10 +692,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1016,13 +1012,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA7A5DA-6C9D-46FC-975A-A9F5DD878FF9}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +1026,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1038,7 +1034,7 @@
         <v>977251.31527214276</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1046,7 +1042,7 @@
         <v>13328055.520714156</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1054,7 +1050,7 @@
         <v>321326687.20403224</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1058,7 @@
         <v>6402511.719496578</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1070,7 +1066,7 @@
         <v>59151603.417757481</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1078,7 +1074,7 @@
         <v>277874999.07853091</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1086,7 +1082,7 @@
         <v>302888.81815348461</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1094,7 +1090,7 @@
         <v>6311801.7126107905</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1102,7 +1098,7 @@
         <v>66709612.957940787</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1106,7 @@
         <v>136545787.17132425</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1118,7 +1114,7 @@
         <v>266622339.29579192</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -1126,7 +1122,7 @@
         <v>3172885.866301666</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>31</v>
       </c>
@@ -1134,7 +1130,7 @@
         <v>438402962.04456699</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -1142,7 +1138,7 @@
         <v>35984585.712862946</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -1150,7 +1146,7 @@
         <v>217521514.44316691</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -1165,26 +1161,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1195,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1206,7 +1203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1217,7 +1214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
@@ -1228,7 +1225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1239,7 +1236,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1250,7 +1247,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1261,7 +1258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1272,7 +1269,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1294,7 +1291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1305,7 +1302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1316,7 +1313,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1327,7 +1324,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1349,7 +1346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1360,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1382,7 +1379,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>29</v>
       </c>
@@ -1393,7 +1390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1404,7 +1401,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1415,7 +1412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1426,7 +1423,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1437,7 +1434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1448,7 +1445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>20</v>
       </c>
@@ -1459,7 +1456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1470,7 +1467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>15</v>
       </c>
@@ -1481,7 +1478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -1492,7 +1489,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1503,7 +1500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>27</v>
       </c>
@@ -1514,7 +1511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1525,7 +1522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -1536,7 +1533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1547,7 +1544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1558,7 +1555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1566,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -1580,7 +1577,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -1591,7 +1588,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -1602,7 +1599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -1613,7 +1610,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>29</v>
       </c>
@@ -1624,7 +1621,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1635,7 +1632,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -1646,7 +1643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -1657,7 +1654,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -1668,7 +1665,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>28</v>
       </c>
@@ -1679,7 +1676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -1690,7 +1687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>19</v>
       </c>
@@ -1701,7 +1698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1712,7 +1709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>28</v>
       </c>
@@ -1723,8 +1720,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:C50" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}"/>
+  <autoFilter ref="A1:C50" xr:uid="{B5B0376C-AE0A-41BC-8998-FF6C9C8BC443}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="HPV"/>
+        <filter val="PCV"/>
+        <filter val="Rotavirus"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
